--- a/output/pdf_financials_xlsx/ONYX.xlsx
+++ b/output/pdf_financials_xlsx/ONYX.xlsx
@@ -618,10 +618,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.098925</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.046868</v>
       </c>
     </row>
     <row r="13">
@@ -876,10 +876,10 @@
         <v>-0.939157</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.223995</v>
+        <v>0.12507</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.389401</v>
+        <v>-1.436269</v>
       </c>
     </row>
     <row r="28">
@@ -908,10 +908,10 @@
         <v>-0.939157</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.223995</v>
+        <v>0.12507</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.367243</v>
+        <v>-1.414111</v>
       </c>
     </row>
     <row r="30">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">

--- a/output/pdf_financials_xlsx/ONYX.xlsx
+++ b/output/pdf_financials_xlsx/ONYX.xlsx
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.004972</v>
       </c>
     </row>
     <row r="111">
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.817123</v>
       </c>
     </row>
     <row r="116">
@@ -3548,7 +3548,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -3614,7 +3618,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -3932,7 +3940,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
